--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.5449494931156</v>
+        <v>11.30105429263129</v>
       </c>
       <c r="D2" t="n">
-        <v>52.17554131114607</v>
+        <v>8.478525463061237</v>
       </c>
       <c r="E2" t="n">
-        <v>15.75348817175524</v>
+        <v>2.559941827910227</v>
       </c>
       <c r="F2" t="n">
-        <v>12.23705500710001</v>
+        <v>1.988521438653752</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.85921595283106</v>
+        <v>11.18962259233505</v>
       </c>
       <c r="D3" t="n">
-        <v>21.49363932026064</v>
+        <v>3.492716389542354</v>
       </c>
       <c r="E3" t="n">
-        <v>15.75348817175524</v>
+        <v>2.559941827910227</v>
       </c>
       <c r="F3" t="n">
-        <v>12.23705500710001</v>
+        <v>1.988521438653752</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.20797289396148</v>
+        <v>9.783795595268741</v>
       </c>
       <c r="D4" t="n">
-        <v>44.59865967094127</v>
+        <v>7.247282196527957</v>
       </c>
       <c r="E4" t="n">
-        <v>15.75348817175524</v>
+        <v>2.559941827910227</v>
       </c>
       <c r="F4" t="n">
-        <v>12.23705500710001</v>
+        <v>1.988521438653752</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.00235843809217</v>
+        <v>8.612883246189977</v>
       </c>
       <c r="D5" t="n">
-        <v>51.39475973083614</v>
+        <v>8.351648456260872</v>
       </c>
       <c r="E5" t="n">
-        <v>15.75348817175524</v>
+        <v>2.559941827910227</v>
       </c>
       <c r="F5" t="n">
-        <v>12.23705500710001</v>
+        <v>1.988521438653752</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.15179979036263</v>
+        <v>6.199667465933928</v>
       </c>
       <c r="D6" t="n">
-        <v>39.35097621909705</v>
+        <v>6.39453363560327</v>
       </c>
       <c r="E6" t="n">
-        <v>15.75348817175524</v>
+        <v>2.559941827910227</v>
       </c>
       <c r="F6" t="n">
-        <v>12.23705500710001</v>
+        <v>1.988521438653752</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.69880272318651</v>
+        <v>4.338555442517808</v>
       </c>
       <c r="D7" t="n">
-        <v>23.7168082818891</v>
+        <v>3.853981345806978</v>
       </c>
       <c r="E7" t="n">
-        <v>15.75348817175524</v>
+        <v>2.559941827910227</v>
       </c>
       <c r="F7" t="n">
-        <v>12.23705500710001</v>
+        <v>1.988521438653752</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
